--- a/excel-files/LAS PINAS/LAS PIÑAS CITY NATIONAL SENIOR HIGH SCHOOL- TALON DOS CAMPUS.xlsx
+++ b/excel-files/LAS PINAS/LAS PIÑAS CITY NATIONAL SENIOR HIGH SCHOOL- TALON DOS CAMPUS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29607"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14B7AF39-B285-4F74-A161-F0CC0FACC674}"/>
+  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4299F131-0424-42A8-8A61-DC128C20E210}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+    <row r="6" spans="1:8" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" ht="15">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
@@ -3707,7 +3707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999">
+    <row r="12" spans="1:8" ht="19.5">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3727,10 +3727,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" ht="15">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999">
+    <row r="19" spans="1:8" ht="19.5">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" ht="15">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999">
+    <row r="23" spans="1:8" ht="19.5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -5402,12 +5402,15 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E92" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E41:E49 E31:E39 E21:E29 E14:E19 E2:E6 E8:E12 E51:E59 E61:E69 E71:E79 E81:E89 E94:E96 E97:E98 E91 E93" xr:uid="{A64A31BF-5E6D-4F52-89AF-C32C90AD3952}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5419,7 +5422,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5591,10 +5594,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="34"/>
-      <c r="L3" s="32">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="5">
         <f t="shared" ref="N3" si="0">IF((J3-K3)&lt;0,0,(J3-K3))</f>
@@ -5641,12 +5641,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J4" s="13"/>
-      <c r="L4" s="7">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="13"/>
@@ -5665,7 +5661,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="38.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5693,10 +5689,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L5" s="32"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
         <f t="shared" ref="N5" si="4">IF((J5-K5)&lt;0,0,(J5-K5))</f>
@@ -5743,7 +5736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5771,10 +5764,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="5"/>
-      <c r="L6" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L6" s="32"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
         <f t="shared" ref="N6:N69" si="10">IF((J6-K6)&lt;0,0,(J6-K6))</f>
@@ -5821,7 +5811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5849,10 +5839,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="5"/>
-      <c r="L7" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L7" s="32"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
         <f t="shared" si="10"/>
@@ -5899,7 +5886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5927,10 +5914,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5"/>
-      <c r="L8" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L8" s="32"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
         <f t="shared" si="10"/>
@@ -5977,7 +5961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6005,10 +5989,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="5"/>
-      <c r="L9" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L9" s="32"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
         <f t="shared" si="10"/>
@@ -6055,7 +6036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6083,10 +6064,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="5"/>
-      <c r="L10" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L10" s="32"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
         <f t="shared" si="10"/>
@@ -6133,7 +6111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6161,10 +6139,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="5"/>
-      <c r="L11" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L11" s="32"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5">
         <f t="shared" si="10"/>
@@ -6211,7 +6186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6239,10 +6214,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="5"/>
-      <c r="L12" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L12" s="32"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
         <f t="shared" si="10"/>
@@ -6289,12 +6261,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J13" s="13"/>
-      <c r="L13" s="7">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
@@ -6314,7 +6282,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6342,10 +6310,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="5"/>
-      <c r="L14" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L14" s="32"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5">
         <f t="shared" si="10"/>
@@ -6392,7 +6357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6420,10 +6385,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="5"/>
-      <c r="L15" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L15" s="32"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5">
         <f t="shared" si="10"/>
@@ -6470,7 +6432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6498,10 +6460,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="5"/>
-      <c r="L16" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L16" s="32"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5">
         <f t="shared" si="10"/>
@@ -6548,7 +6507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6576,10 +6535,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="5"/>
-      <c r="L17" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L17" s="32"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5">
         <f t="shared" si="10"/>
@@ -6626,7 +6582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6654,10 +6610,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L18" s="32"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
         <f t="shared" si="10"/>
@@ -6704,7 +6657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6732,10 +6685,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="5"/>
-      <c r="L19" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L19" s="32"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
         <f t="shared" si="10"/>
@@ -6782,7 +6732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6810,10 +6760,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="5"/>
-      <c r="L20" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L20" s="32"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5">
         <f t="shared" si="10"/>
@@ -6860,7 +6807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6888,10 +6835,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="5"/>
-      <c r="L21" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L21" s="32"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
         <f t="shared" si="10"/>
@@ -6938,12 +6882,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J22" s="13"/>
-      <c r="L22" s="7">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
@@ -6964,7 +6904,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6992,10 +6932,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="5"/>
-      <c r="L23" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L23" s="32"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5">
         <f t="shared" si="10"/>
@@ -7042,7 +6979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7070,10 +7007,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="5"/>
-      <c r="L24" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L24" s="32"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5">
         <f t="shared" si="10"/>
@@ -7120,7 +7054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7148,10 +7082,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="5"/>
-      <c r="L25" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L25" s="32"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5">
         <f t="shared" si="10"/>
@@ -7198,7 +7129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7226,10 +7157,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="5"/>
-      <c r="L26" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L26" s="32"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5">
         <f t="shared" si="10"/>
@@ -7276,7 +7204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7304,10 +7232,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="5"/>
-      <c r="L27" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L27" s="32"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
         <f t="shared" si="10"/>
@@ -7354,7 +7279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7382,10 +7307,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="5"/>
-      <c r="L28" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L28" s="32"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
         <f t="shared" si="10"/>
@@ -7432,7 +7354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7460,10 +7382,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="5"/>
-      <c r="L29" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L29" s="32"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
         <f t="shared" si="10"/>
@@ -7510,7 +7429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7538,10 +7457,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="5"/>
-      <c r="L30" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L30" s="32"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5">
         <f t="shared" si="10"/>
@@ -7588,7 +7504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7616,10 +7532,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="5"/>
-      <c r="L31" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L31" s="32"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5">
         <f t="shared" si="10"/>
@@ -7666,12 +7579,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J32" s="13"/>
-      <c r="L32" s="7">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
       <c r="O32" s="13"/>
@@ -7692,7 +7601,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7720,10 +7629,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="5"/>
-      <c r="L33" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L33" s="32"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5">
         <f t="shared" si="10"/>
@@ -7770,7 +7676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7798,10 +7704,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="5"/>
-      <c r="L34" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L34" s="32"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5">
         <f t="shared" si="10"/>
@@ -7848,7 +7751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7876,10 +7779,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="5"/>
-      <c r="L35" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L35" s="32"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5">
         <f t="shared" si="10"/>
@@ -7926,7 +7826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7954,10 +7854,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="5"/>
-      <c r="L36" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L36" s="32"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5">
         <f t="shared" si="10"/>
@@ -8004,7 +7901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -8032,10 +7929,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="5"/>
-      <c r="L37" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L37" s="32"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5">
         <f t="shared" si="10"/>
@@ -8082,7 +7976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -8110,10 +8004,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="5"/>
-      <c r="L38" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L38" s="32"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5">
         <f t="shared" si="10"/>
@@ -8160,7 +8051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8188,10 +8079,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="5"/>
-      <c r="L39" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L39" s="32"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5">
         <f t="shared" si="10"/>
@@ -8238,7 +8126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8266,10 +8154,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="5"/>
-      <c r="L40" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L40" s="32"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5">
         <f t="shared" si="10"/>
@@ -8316,7 +8201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8344,10 +8229,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="5"/>
-      <c r="L41" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L41" s="32"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5">
         <f t="shared" si="10"/>
@@ -8394,12 +8276,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J42" s="13"/>
-      <c r="L42" s="7">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
       <c r="O42" s="13"/>
@@ -8420,7 +8298,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8448,10 +8326,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="5"/>
-      <c r="L43" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L43" s="32"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5">
         <f t="shared" si="10"/>
@@ -8498,7 +8373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8526,10 +8401,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="5"/>
-      <c r="L44" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L44" s="32"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5">
         <f t="shared" si="10"/>
@@ -8576,7 +8448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8604,10 +8476,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="5"/>
-      <c r="L45" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L45" s="32"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5">
         <f t="shared" si="10"/>
@@ -8654,7 +8523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8682,10 +8551,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="5"/>
-      <c r="L46" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L46" s="32"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
         <f t="shared" si="10"/>
@@ -8732,7 +8598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8760,10 +8626,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="5"/>
-      <c r="L47" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L47" s="32"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
         <f t="shared" si="10"/>
@@ -8810,7 +8673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8838,10 +8701,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="5"/>
-      <c r="L48" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L48" s="32"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
         <f t="shared" si="10"/>
@@ -8888,7 +8748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8916,10 +8776,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="5"/>
-      <c r="L49" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L49" s="32"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5">
         <f t="shared" si="10"/>
@@ -8966,7 +8823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8994,10 +8851,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="5"/>
-      <c r="L50" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L50" s="32"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
         <f t="shared" si="10"/>
@@ -9044,7 +8898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -9072,10 +8926,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="5"/>
-      <c r="L51" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L51" s="32"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
         <f t="shared" si="10"/>
@@ -9122,12 +8973,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J52" s="13"/>
-      <c r="L52" s="7">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
       <c r="O52" s="13"/>
@@ -9148,7 +8995,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -9176,10 +9023,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="5"/>
-      <c r="L53" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L53" s="32"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
         <f t="shared" si="10"/>
@@ -9226,7 +9070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -9254,10 +9098,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="5"/>
-      <c r="L54" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L54" s="32"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5">
         <f t="shared" si="10"/>
@@ -9304,7 +9145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9332,10 +9173,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="5"/>
-      <c r="L55" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L55" s="32"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5">
         <f t="shared" si="10"/>
@@ -9382,7 +9220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9410,10 +9248,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="5"/>
-      <c r="L56" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L56" s="32"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5">
         <f t="shared" si="10"/>
@@ -9460,7 +9295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9488,10 +9323,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="5"/>
-      <c r="L57" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L57" s="32"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5">
         <f t="shared" si="10"/>
@@ -9538,7 +9370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9566,10 +9398,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="5"/>
-      <c r="L58" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L58" s="32"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
         <f t="shared" si="10"/>
@@ -9616,7 +9445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9644,10 +9473,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="5"/>
-      <c r="L59" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L59" s="32"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5">
         <f t="shared" si="10"/>
@@ -9694,7 +9520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9722,10 +9548,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="5"/>
-      <c r="L60" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L60" s="32"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5">
         <f t="shared" si="10"/>
@@ -9772,7 +9595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9800,10 +9623,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="5"/>
-      <c r="L61" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L61" s="32"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5">
         <f t="shared" si="10"/>
@@ -9852,10 +9672,6 @@
     </row>
     <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J62" s="13"/>
-      <c r="L62" s="7">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
       <c r="O62" s="13"/>
@@ -9876,7 +9692,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9904,10 +9720,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="12"/>
-      <c r="L63" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L63" s="10"/>
       <c r="M63" s="12"/>
       <c r="N63" s="12">
         <f t="shared" si="10"/>
@@ -9954,7 +9767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9982,10 +9795,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="12"/>
-      <c r="L64" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L64" s="10"/>
       <c r="M64" s="12"/>
       <c r="N64" s="12">
         <f t="shared" si="10"/>
@@ -10032,7 +9842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -10060,10 +9870,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="12"/>
-      <c r="L65" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L65" s="10"/>
       <c r="M65" s="12"/>
       <c r="N65" s="12">
         <f t="shared" si="10"/>
@@ -10110,7 +9917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -10138,10 +9945,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="12"/>
-      <c r="L66" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L66" s="10"/>
       <c r="M66" s="12"/>
       <c r="N66" s="12">
         <f t="shared" si="10"/>
@@ -10188,7 +9992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -10216,10 +10020,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="12"/>
-      <c r="L67" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L67" s="10"/>
       <c r="M67" s="12"/>
       <c r="N67" s="12">
         <f t="shared" si="10"/>
@@ -10266,7 +10067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -10294,10 +10095,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="12"/>
-      <c r="L68" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L68" s="10"/>
       <c r="M68" s="12"/>
       <c r="N68" s="12">
         <f t="shared" si="10"/>
@@ -10344,7 +10142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -10372,10 +10170,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="12"/>
-      <c r="L69" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L69" s="10"/>
       <c r="M69" s="12"/>
       <c r="N69" s="12">
         <f t="shared" si="10"/>
@@ -10422,7 +10217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -10450,10 +10245,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="12"/>
-      <c r="L70" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L70" s="10"/>
       <c r="M70" s="12"/>
       <c r="N70" s="12">
         <f t="shared" ref="N70:N126" si="16">IF((J70-K70)&lt;0,0,(J70-K70))</f>
@@ -10500,7 +10292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10528,10 +10320,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="12"/>
-      <c r="L71" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L71" s="10"/>
       <c r="M71" s="12"/>
       <c r="N71" s="12">
         <f t="shared" si="16"/>
@@ -10580,10 +10369,6 @@
     </row>
     <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J72" s="13"/>
-      <c r="L72" s="7">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
       <c r="O72" s="13"/>
@@ -10604,7 +10389,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10632,10 +10417,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="12"/>
-      <c r="L73" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L73" s="10"/>
       <c r="M73" s="12"/>
       <c r="N73" s="12">
         <f t="shared" si="16"/>
@@ -10682,7 +10464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10710,10 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="12"/>
-      <c r="L74" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L74" s="10"/>
       <c r="M74" s="12"/>
       <c r="N74" s="12">
         <f t="shared" si="16"/>
@@ -10760,7 +10539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10788,10 +10567,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="12"/>
-      <c r="L75" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L75" s="10"/>
       <c r="M75" s="12"/>
       <c r="N75" s="12">
         <f t="shared" si="16"/>
@@ -10838,7 +10614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10866,10 +10642,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="12"/>
-      <c r="L76" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L76" s="10"/>
       <c r="M76" s="12"/>
       <c r="N76" s="12">
         <f t="shared" si="16"/>
@@ -10916,7 +10689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10944,10 +10717,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="12"/>
-      <c r="L77" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L77" s="10"/>
       <c r="M77" s="12"/>
       <c r="N77" s="12">
         <f t="shared" si="16"/>
@@ -10994,7 +10764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -11022,10 +10792,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="12"/>
-      <c r="L78" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L78" s="10"/>
       <c r="M78" s="12"/>
       <c r="N78" s="12">
         <f t="shared" si="16"/>
@@ -11072,7 +10839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -11100,10 +10867,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="12"/>
-      <c r="L79" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
         <f t="shared" si="16"/>
@@ -11150,7 +10914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -11178,10 +10942,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="12"/>
-      <c r="L80" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L80" s="10"/>
       <c r="M80" s="12"/>
       <c r="N80" s="12">
         <f t="shared" si="16"/>
@@ -11228,7 +10989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -11256,10 +11017,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="12"/>
-      <c r="L81" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L81" s="10"/>
       <c r="M81" s="12"/>
       <c r="N81" s="12">
         <f t="shared" si="16"/>
@@ -11306,12 +11064,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
-      <c r="L82" s="7">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
       <c r="O82" s="13"/>
@@ -11332,7 +11086,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -11360,10 +11114,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="12"/>
-      <c r="L83" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L83" s="10"/>
       <c r="M83" s="12"/>
       <c r="N83" s="12">
         <f t="shared" si="16"/>
@@ -11410,7 +11161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -11438,10 +11189,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="12"/>
-      <c r="L84" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L84" s="10"/>
       <c r="M84" s="12"/>
       <c r="N84" s="12">
         <f t="shared" si="16"/>
@@ -11488,7 +11236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -11516,10 +11264,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="12"/>
-      <c r="L85" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L85" s="10"/>
       <c r="M85" s="12"/>
       <c r="N85" s="12">
         <f t="shared" si="16"/>
@@ -11566,7 +11311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -11594,10 +11339,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="12"/>
-      <c r="L86" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L86" s="10"/>
       <c r="M86" s="12"/>
       <c r="N86" s="12">
         <f t="shared" si="16"/>
@@ -11644,7 +11386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11672,10 +11414,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="12"/>
-      <c r="L87" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L87" s="10"/>
       <c r="M87" s="12"/>
       <c r="N87" s="12">
         <f t="shared" si="16"/>
@@ -11722,7 +11461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11750,10 +11489,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="12"/>
-      <c r="L88" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L88" s="10"/>
       <c r="M88" s="12"/>
       <c r="N88" s="12">
         <f t="shared" si="16"/>
@@ -11800,7 +11536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11828,10 +11564,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="12"/>
-      <c r="L89" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L89" s="10"/>
       <c r="M89" s="12"/>
       <c r="N89" s="12">
         <f t="shared" si="16"/>
@@ -11878,7 +11611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11906,10 +11639,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="12"/>
-      <c r="L90" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L90" s="10"/>
       <c r="M90" s="12"/>
       <c r="N90" s="12">
         <f t="shared" si="16"/>
@@ -11956,7 +11686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11984,10 +11714,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="12"/>
-      <c r="L91" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L91" s="10"/>
       <c r="M91" s="12"/>
       <c r="N91" s="12">
         <f t="shared" si="16"/>
@@ -12034,12 +11761,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J92" s="13"/>
-      <c r="L92" s="7">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
       <c r="O92" s="13"/>
@@ -12060,7 +11783,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -12088,10 +11811,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="12"/>
-      <c r="L93" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L93" s="10"/>
       <c r="M93" s="12"/>
       <c r="N93" s="12">
         <f>IF((J93-K93)&lt;0,0,(J93-K93))</f>
@@ -12138,7 +11858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -12166,10 +11886,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="12"/>
-      <c r="L94" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L94" s="10"/>
       <c r="M94" s="12"/>
       <c r="N94" s="12">
         <f>IF((J94-K94)&lt;0,0,(J94-K94))</f>
@@ -12216,7 +11933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -12244,10 +11961,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="12"/>
-      <c r="L95" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L95" s="10"/>
       <c r="M95" s="12"/>
       <c r="N95" s="12">
         <f>IF((J95-K95)&lt;0,0,(J95-K95))</f>
@@ -12294,7 +12008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -12322,10 +12036,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="12"/>
-      <c r="L96" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L96" s="10"/>
       <c r="M96" s="12"/>
       <c r="N96" s="12">
         <f>IF((J96-K96)&lt;0,0,(J96-K96))</f>
@@ -12372,7 +12083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -12400,10 +12111,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="12"/>
-      <c r="L97" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L97" s="10"/>
       <c r="M97" s="12"/>
       <c r="N97" s="12">
         <f>IF((J97-K97)&lt;0,0,(J97-K97))</f>
@@ -12450,7 +12158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -12478,10 +12186,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="12"/>
-      <c r="L98" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L98" s="10"/>
       <c r="M98" s="12"/>
       <c r="N98" s="12">
         <f>IF((J98-K98)&lt;0,0,(J98-K98))</f>
@@ -12528,7 +12233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -12556,10 +12261,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="12"/>
-      <c r="L99" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L99" s="10"/>
       <c r="M99" s="12"/>
       <c r="N99" s="12">
         <f>IF((J99-K99)&lt;0,0,(J99-K99))</f>
@@ -12606,7 +12308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -12634,10 +12336,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="12"/>
-      <c r="L100" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L100" s="10"/>
       <c r="M100" s="12"/>
       <c r="N100" s="12">
         <f>IF((J100-K100)&lt;0,0,(J100-K100))</f>
@@ -12684,7 +12383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -12712,10 +12411,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="12"/>
-      <c r="L101" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L101" s="10"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12">
         <f>IF((J101-K101)&lt;0,0,(J101-K101))</f>
@@ -12764,10 +12460,6 @@
     </row>
     <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J102" s="13"/>
-      <c r="L102" s="7">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
       <c r="O102" s="13"/>
@@ -13570,10 +13262,6 @@
     </row>
     <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J111" s="13"/>
-      <c r="L111" s="7">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
       <c r="P111" s="13"/>
@@ -13591,7 +13279,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -13612,10 +13300,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="5"/>
-      <c r="L112" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L112" s="1"/>
       <c r="M112" s="5"/>
       <c r="N112" s="5">
         <f t="shared" si="16"/>
@@ -13662,7 +13347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -13683,10 +13368,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="5"/>
-      <c r="L113" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L113" s="1"/>
       <c r="M113" s="5"/>
       <c r="N113" s="5">
         <f t="shared" si="16"/>
@@ -13733,7 +13415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -13754,10 +13436,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="5"/>
-      <c r="L114" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L114" s="1"/>
       <c r="M114" s="5"/>
       <c r="N114" s="5">
         <f t="shared" si="16"/>
@@ -13804,7 +13483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -13825,10 +13504,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="5"/>
-      <c r="L115" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L115" s="1"/>
       <c r="M115" s="5"/>
       <c r="N115" s="5">
         <f t="shared" si="16"/>
@@ -13875,7 +13551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -13896,10 +13572,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="5"/>
-      <c r="L116" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L116" s="1"/>
       <c r="M116" s="5"/>
       <c r="N116" s="5">
         <f t="shared" si="16"/>
@@ -13946,7 +13619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -13967,10 +13640,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="5"/>
-      <c r="L117" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L117" s="1"/>
       <c r="M117" s="5"/>
       <c r="N117" s="5">
         <f t="shared" si="16"/>
@@ -14017,7 +13687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -14038,10 +13708,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="5"/>
-      <c r="L118" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L118" s="1"/>
       <c r="M118" s="5"/>
       <c r="N118" s="5">
         <f t="shared" si="16"/>
@@ -14088,7 +13755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -14109,10 +13776,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="5"/>
-      <c r="L119" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L119" s="1"/>
       <c r="M119" s="5"/>
       <c r="N119" s="5">
         <f t="shared" si="16"/>
@@ -14159,7 +13823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -14180,10 +13844,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="5"/>
-      <c r="L120" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L120" s="1"/>
       <c r="M120" s="5"/>
       <c r="N120" s="5">
         <f t="shared" si="16"/>
@@ -14230,7 +13891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -14251,10 +13912,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="5"/>
-      <c r="L121" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L121" s="1"/>
       <c r="M121" s="5"/>
       <c r="N121" s="5">
         <f t="shared" si="16"/>
@@ -14301,7 +13959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -14322,10 +13980,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="5"/>
-      <c r="L122" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L122" s="1"/>
       <c r="M122" s="5"/>
       <c r="N122" s="5">
         <f t="shared" si="16"/>
@@ -14372,7 +14027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -14393,10 +14048,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="5"/>
-      <c r="L123" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L123" s="1"/>
       <c r="M123" s="5"/>
       <c r="N123" s="5">
         <f t="shared" si="16"/>
@@ -14443,7 +14095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -14464,10 +14116,7 @@
         <v>0</v>
       </c>
       <c r="K124" s="5"/>
-      <c r="L124" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L124" s="1"/>
       <c r="M124" s="5"/>
       <c r="N124" s="5">
         <f t="shared" si="16"/>
@@ -14514,7 +14163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -14535,10 +14184,7 @@
         <v>0</v>
       </c>
       <c r="K125" s="5"/>
-      <c r="L125" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L125" s="1"/>
       <c r="M125" s="5"/>
       <c r="N125" s="5">
         <f t="shared" si="16"/>
@@ -14585,7 +14231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -14606,10 +14252,7 @@
         <v>0</v>
       </c>
       <c r="K126" s="5"/>
-      <c r="L126" s="1">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L126" s="1"/>
       <c r="M126" s="5"/>
       <c r="N126" s="5">
         <f t="shared" si="16"/>
@@ -14656,13 +14299,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
       <c r="D127" s="5"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="29"/>
+      <c r="F127" s="1"/>
       <c r="G127" s="31"/>
       <c r="H127" s="5">
         <f t="shared" si="22"/>
@@ -14677,10 +14320,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="31"/>
-      <c r="L127" s="29">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
+      <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -14692,7 +14332,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29">
+      <c r="R127" s="1">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
@@ -14710,7 +14350,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="31"/>
-      <c r="X127" s="29">
+      <c r="X127" s="1">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
@@ -14724,190 +14364,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12 K103:K110 Q103:Q110 W103:W110" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 L103:L110 R103:R110 X103:X110" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H33:I41 H43:I51 H53:I61 H63:I71 H73:I81 H83:I91 H93:I101 D103:F110 H103:I110 H112:I127 N127:Q127 H14:I21 H23:I31 H6:I12 Q112:R112 P2:R2 V2:X3 N13:P126 J6:J127 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 L103:L110 X103:X110 D5:F12 D14:F21 H5:L5 K43:L51 K53:L61 K63:L71 K6:L12 K14:L21 K23:L31 K33:L41 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71 Q73:R81 Q83:R91 Q93:R101 R103:R110 Q113:Q126 R113:R127 W33:X41 W43:X51 W53:X61 W63:X71 W73:X81 W83:X91 W93:X101 D23:F31 D33:F41 D43:F51 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D112:F127 K73:L81 K83:L91 K93:L101 K112:L127 T13:V127 N5:R12 T5:X12 W14:X21 W23:X31 W112:X127" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 Y5:Y12 G14:G21 M3 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 M14:M110 S4:S110 Y14:Y110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -14917,16 +14377,20 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F103:F110" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G103:G110 S4:S110 M14:M110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 Y14:Y110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 X23:X31 L3 L33:L41 L43:L51 L53:L61 L63:L71 L14:L21 L5:L12 L23:L31 L112:L127 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R112:R127 R5:R12 X5:X12 X14:X21 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 F23:F61 F63:F71 F73:F81 F83:F91 F93:F101 F112:F127 L73:L81 L83:L91 L93:L101 X112:X127" xr:uid="{064B2FB7-2E07-40BE-A420-F312394B8D1D}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K12 K14:K21 K23:K31" xr:uid="{3E2ECECB-5A74-4DA2-822D-6FF19BE7A36F}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
